--- a/重大节点进度追踪通报及存档汇总/土建完成节点汇总v2_20260805.xlsx
+++ b/重大节点进度追踪通报及存档汇总/土建完成节点汇总v2_20260805.xlsx
@@ -705,7 +705,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -721,6 +721,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1047,7 +1053,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1071,16 +1077,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1089,89 +1095,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1192,6 +1198,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1918,7 +1930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="17" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -1938,7 +1950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="18" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -1958,7 +1970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="19" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -1978,7 +1990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="20" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -1998,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="21" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2018,7 +2030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="22" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2038,7 +2050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="23" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2058,7 +2070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="24" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2078,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="25" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2098,7 +2110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="26" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2118,7 +2130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="27" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2138,7 +2150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="28" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -2158,7 +2170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="29" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -2178,7 +2190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="30" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -2198,7 +2210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="31" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2218,47 +2230,51 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
-      <c r="A32" s="4">
+    <row r="32" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
+      <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
-      <c r="A33" s="4">
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
+      <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -2278,47 +2294,51 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
-      <c r="A35" s="4">
+    <row r="35" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
+      <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
-      <c r="A36" s="4">
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
+      <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="9">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2338,7 +2358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="38" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -2358,7 +2378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="39" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2378,7 +2398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="40" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -2398,7 +2418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="41" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2418,7 +2438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="42" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -2438,7 +2458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="43" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2458,7 +2478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="44" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -2478,7 +2498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="45" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2498,7 +2518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="46" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -2518,7 +2538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="47" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2538,7 +2558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
+    <row r="48" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -2602,23 +2622,23 @@
       <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="6">
         <v>1</v>
       </c>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A52" s="4">
@@ -2821,24 +2841,26 @@
       </c>
     </row>
     <row r="62" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
-      <c r="A62" s="4">
+      <c r="A62" s="7">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="7">
         <v>5</v>
       </c>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
     </row>
     <row r="63" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A63" s="4">
@@ -2861,24 +2883,26 @@
       </c>
     </row>
     <row r="64" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
-      <c r="A64" s="4">
+      <c r="A64" s="7">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="7">
         <v>5</v>
       </c>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
     </row>
     <row r="65" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
       <c r="A65" s="4">

--- a/重大节点进度追踪通报及存档汇总/土建完成节点汇总v2_20260805.xlsx
+++ b/重大节点进度追踪通报及存档汇总/土建完成节点汇总v2_20260805.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="土建完成节点汇总" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">土建完成节点汇总!$A$1:$H$134</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="170">
   <si>
     <t>序号</t>
   </si>
@@ -196,6 +199,12 @@
     <t>28-36轴6.0M标高圈梁浇筑</t>
   </si>
   <si>
+    <t>完成度20%</t>
+  </si>
+  <si>
+    <t>兰江</t>
+  </si>
+  <si>
     <t>干煤棚承台5轴交k轴</t>
   </si>
   <si>
@@ -281,6 +290,9 @@
   </si>
   <si>
     <t>28-36轴9.0M标高楼面浇筑</t>
+  </si>
+  <si>
+    <t>完成度60%</t>
   </si>
   <si>
     <t>输渣沟剩余部分土方开挖</t>
@@ -705,7 +717,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -721,12 +733,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,7 +1059,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1077,16 +1083,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1095,89 +1101,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1200,10 +1206,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2234,45 +2237,49 @@
       <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="7">
         <v>8</v>
       </c>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="G32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
-      <c r="A33" s="9">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="6">
         <v>1</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A34" s="4">
@@ -2298,45 +2305,49 @@
       <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="7">
         <v>8</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="G35" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
-      <c r="A36" s="9">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="C36" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="6">
         <v>7</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A37" s="4">
@@ -2346,7 +2357,7 @@
         <v>18</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>20</v>
@@ -2366,7 +2377,7 @@
         <v>18</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>13</v>
@@ -2386,13 +2397,13 @@
         <v>26</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
@@ -2406,13 +2417,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F40" s="1">
         <v>6</v>
@@ -2426,13 +2437,13 @@
         <v>11</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F41" s="1">
         <v>8</v>
@@ -2446,13 +2457,13 @@
         <v>40</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F42" s="1">
         <v>2</v>
@@ -2466,13 +2477,13 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F43" s="1">
         <v>10</v>
@@ -2486,13 +2497,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -2506,13 +2517,13 @@
         <v>18</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F45" s="1">
         <v>5</v>
@@ -2526,13 +2537,13 @@
         <v>11</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F46" s="1">
         <v>7</v>
@@ -2546,13 +2557,13 @@
         <v>40</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F47" s="1">
         <v>5</v>
@@ -2566,13 +2577,13 @@
         <v>26</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F48" s="1">
         <v>2</v>
@@ -2586,13 +2597,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F49" s="1">
         <v>10</v>
@@ -2606,13 +2617,13 @@
         <v>40</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F50" s="1">
         <v>4</v>
@@ -2626,13 +2637,13 @@
         <v>40</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F51" s="6">
         <v>1</v>
@@ -2648,13 +2659,13 @@
         <v>26</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -2668,13 +2679,13 @@
         <v>29</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F53" s="1">
         <v>5</v>
@@ -2688,13 +2699,13 @@
         <v>8</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="F54" s="1">
         <v>4</v>
@@ -2708,13 +2719,13 @@
         <v>8</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F55" s="1">
         <v>10</v>
@@ -2728,13 +2739,13 @@
         <v>47</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="F56" s="1">
         <v>4</v>
@@ -2748,13 +2759,13 @@
         <v>47</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F57" s="1">
         <v>10</v>
@@ -2768,13 +2779,13 @@
         <v>32</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F58" s="1">
         <v>5</v>
@@ -2788,13 +2799,13 @@
         <v>40</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
@@ -2808,13 +2819,13 @@
         <v>26</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -2828,13 +2839,13 @@
         <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F61" s="1">
         <v>2</v>
@@ -2848,19 +2859,23 @@
         <v>8</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="F62" s="7">
         <v>5</v>
       </c>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
+      <c r="G62" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="63" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A63" s="4">
@@ -2870,13 +2885,13 @@
         <v>47</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -2890,19 +2905,23 @@
         <v>47</v>
       </c>
       <c r="C64" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="F64" s="7">
         <v>5</v>
       </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
+      <c r="G64" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="65" s="1" customFormat="1" ht="31" customHeight="1" spans="1:6">
       <c r="A65" s="4">
@@ -2912,13 +2931,13 @@
         <v>40</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F65" s="1">
         <v>2</v>
@@ -2932,13 +2951,13 @@
         <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
@@ -2952,13 +2971,13 @@
         <v>47</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F67" s="1">
         <v>6</v>
@@ -2972,13 +2991,13 @@
         <v>47</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
@@ -2992,13 +3011,13 @@
         <v>40</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F69" s="1">
         <v>3</v>
@@ -3012,13 +3031,13 @@
         <v>40</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -3032,13 +3051,13 @@
         <v>47</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
@@ -3052,13 +3071,13 @@
         <v>8</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F72" s="1">
         <v>6</v>
@@ -3072,13 +3091,13 @@
         <v>18</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F73" s="1">
         <v>10</v>
@@ -3092,13 +3111,13 @@
         <v>40</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -3112,13 +3131,13 @@
         <v>29</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F75" s="1">
         <v>5</v>
@@ -3132,13 +3151,13 @@
         <v>8</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F76" s="1">
         <v>3</v>
@@ -3152,13 +3171,13 @@
         <v>32</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F77" s="1">
         <v>5</v>
@@ -3172,13 +3191,13 @@
         <v>40</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F78" s="1">
         <v>5</v>
@@ -3192,13 +3211,13 @@
         <v>40</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="F79" s="1">
         <v>3</v>
@@ -3212,13 +3231,13 @@
         <v>18</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F80" s="1">
         <v>10</v>
@@ -3232,13 +3251,13 @@
         <v>8</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F81" s="1">
         <v>6</v>
@@ -3252,13 +3271,13 @@
         <v>47</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F82" s="1">
         <v>6</v>
@@ -3272,13 +3291,13 @@
         <v>26</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F83" s="1">
         <v>6</v>
@@ -3292,13 +3311,13 @@
         <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F84" s="1">
         <v>6</v>
@@ -3312,13 +3331,13 @@
         <v>8</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F85" s="1">
         <v>8</v>
@@ -3332,13 +3351,13 @@
         <v>47</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F86" s="1">
         <v>6</v>
@@ -3352,13 +3371,13 @@
         <v>47</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F87" s="1">
         <v>8</v>
@@ -3372,13 +3391,13 @@
         <v>18</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="F88" s="1">
         <v>10</v>
@@ -3392,13 +3411,13 @@
         <v>40</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F89" s="1">
         <v>4</v>
@@ -3412,13 +3431,13 @@
         <v>8</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
@@ -3432,13 +3451,13 @@
         <v>47</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F91" s="1">
         <v>6</v>
@@ -3452,13 +3471,13 @@
         <v>47</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -3472,13 +3491,13 @@
         <v>40</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F93" s="1">
         <v>4</v>
@@ -3492,13 +3511,13 @@
         <v>29</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F94" s="1">
         <v>5</v>
@@ -3512,13 +3531,13 @@
         <v>18</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F95" s="1">
         <v>2</v>
@@ -3532,13 +3551,13 @@
         <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F96" s="1">
         <v>5</v>
@@ -3552,13 +3571,13 @@
         <v>40</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F97" s="1">
         <v>2</v>
@@ -3572,13 +3591,13 @@
         <v>40</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="F98" s="1">
         <v>5</v>
@@ -3592,13 +3611,13 @@
         <v>47</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F99" s="1">
         <v>3</v>
@@ -3612,13 +3631,13 @@
         <v>8</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F100" s="1">
         <v>10</v>
@@ -3632,13 +3651,13 @@
         <v>26</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F101" s="1">
         <v>6</v>
@@ -3652,13 +3671,13 @@
         <v>29</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F102" s="1">
         <v>5</v>
@@ -3672,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="F103" s="1">
         <v>6</v>
@@ -3692,13 +3711,13 @@
         <v>47</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="F104" s="1">
         <v>6</v>
@@ -3712,13 +3731,13 @@
         <v>32</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F105" s="1">
         <v>5</v>
@@ -3732,13 +3751,13 @@
         <v>26</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F106" s="1">
         <v>2</v>
@@ -3752,13 +3771,13 @@
         <v>8</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F107" s="1">
         <v>3</v>
@@ -3772,13 +3791,13 @@
         <v>8</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F108" s="1">
         <v>10</v>
@@ -3792,13 +3811,13 @@
         <v>47</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F109" s="1">
         <v>3</v>
@@ -3812,13 +3831,13 @@
         <v>47</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F110" s="1">
         <v>10</v>
@@ -3832,13 +3851,13 @@
         <v>8</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F111" s="1">
         <v>10</v>
@@ -3852,13 +3871,13 @@
         <v>47</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F112" s="1">
         <v>10</v>
@@ -3872,13 +3891,13 @@
         <v>8</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F113" s="1">
         <v>6</v>
@@ -3892,13 +3911,13 @@
         <v>18</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F114" s="1">
         <v>10</v>
@@ -3912,13 +3931,13 @@
         <v>26</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F115" s="1">
         <v>4</v>
@@ -3932,13 +3951,13 @@
         <v>29</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F116" s="1">
         <v>6</v>
@@ -3952,13 +3971,13 @@
         <v>18</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F117" s="1">
         <v>35</v>
@@ -3972,13 +3991,13 @@
         <v>32</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F118" s="1">
         <v>6</v>
@@ -3992,13 +4011,13 @@
         <v>47</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F119" s="1">
         <v>10</v>
@@ -4012,13 +4031,13 @@
         <v>18</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F120" s="1">
         <v>3</v>
@@ -4032,13 +4051,13 @@
         <v>8</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F121" s="1">
         <v>6</v>
@@ -4052,13 +4071,13 @@
         <v>8</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F122" s="1">
         <v>10</v>
@@ -4072,13 +4091,13 @@
         <v>47</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F123" s="1">
         <v>10</v>
@@ -4092,13 +4111,13 @@
         <v>8</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F124" s="1">
         <v>10</v>
@@ -4112,13 +4131,13 @@
         <v>47</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F125" s="1">
         <v>10</v>
@@ -4132,13 +4151,13 @@
         <v>47</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F126" s="1">
         <v>6</v>
@@ -4152,13 +4171,13 @@
         <v>18</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F127" s="1">
         <v>5</v>
@@ -4172,13 +4191,13 @@
         <v>18</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F128" s="1">
         <v>3</v>
@@ -4192,13 +4211,13 @@
         <v>47</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F129" s="1">
         <v>6</v>
@@ -4212,13 +4231,13 @@
         <v>47</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F130" s="1">
         <v>6</v>
@@ -4232,13 +4251,13 @@
         <v>18</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F131" s="1">
         <v>50</v>
@@ -4252,13 +4271,13 @@
         <v>47</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F132" s="1">
         <v>6</v>
@@ -4272,13 +4291,13 @@
         <v>47</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F133" s="1">
         <v>10</v>
@@ -4292,23 +4311,26 @@
         <v>47</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F134" s="1">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H134" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F134" numberStoredAsText="1"/>
+    <ignoredError sqref="A65:F134 D64:F64 A64:B64 A63:F63 D62:F62 A62:B62 A36:F61 D35:F35 A35:B35 A33:F34 D32:F32 A32:B32 A2:F31 A1 C1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/重大节点进度追踪通报及存档汇总/土建完成节点汇总v2_20260805.xlsx
+++ b/重大节点进度追踪通报及存档汇总/土建完成节点汇总v2_20260805.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="171">
   <si>
     <t>序号</t>
   </si>
@@ -199,7 +199,7 @@
     <t>28-36轴6.0M标高圈梁浇筑</t>
   </si>
   <si>
-    <t>完成度20%</t>
+    <t>完成度100%</t>
   </si>
   <si>
     <t>兰江</t>
@@ -277,6 +277,9 @@
     <t>18-28轴6.0M标高楼面浇筑</t>
   </si>
   <si>
+    <t>完成度40%</t>
+  </si>
+  <si>
     <t>主厂房锅炉处地面浇筑垫层</t>
   </si>
   <si>
@@ -292,7 +295,7 @@
     <t>28-36轴9.0M标高楼面浇筑</t>
   </si>
   <si>
-    <t>完成度60%</t>
+    <t>完成度90%</t>
   </si>
   <si>
     <t>输渣沟剩余部分土方开挖</t>
@@ -717,7 +720,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -733,6 +736,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1059,7 +1068,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1083,16 +1092,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1101,89 +1110,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1204,6 +1213,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2712,23 +2724,29 @@
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
-      <c r="A55" s="4">
+      <c r="A55" s="7">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="8">
         <v>10</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
@@ -2752,23 +2770,29 @@
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
-      <c r="A57" s="4">
+      <c r="A57" s="7">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="8">
         <v>10</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
@@ -2799,7 +2823,7 @@
         <v>40</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>66</v>
@@ -2819,13 +2843,13 @@
         <v>26</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -2839,13 +2863,13 @@
         <v>8</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F61" s="1">
         <v>2</v>
@@ -2859,19 +2883,19 @@
         <v>8</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F62" s="7">
         <v>5</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>85</v>
+      <c r="G62" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>55</v>
@@ -2885,13 +2909,13 @@
         <v>47</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -2905,19 +2929,19 @@
         <v>47</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F64" s="7">
         <v>5</v>
       </c>
-      <c r="G64" s="8" t="s">
-        <v>85</v>
+      <c r="G64" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>55</v>
@@ -2931,13 +2955,13 @@
         <v>40</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F65" s="1">
         <v>2</v>
@@ -2951,13 +2975,13 @@
         <v>8</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
@@ -2977,7 +3001,7 @@
         <v>60</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F67" s="1">
         <v>6</v>
@@ -2991,13 +3015,13 @@
         <v>47</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F68" s="1">
         <v>1</v>
@@ -3011,13 +3035,13 @@
         <v>40</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F69" s="1">
         <v>3</v>
@@ -3031,13 +3055,13 @@
         <v>40</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -3054,10 +3078,10 @@
         <v>65</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
@@ -3071,13 +3095,13 @@
         <v>8</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F72" s="1">
         <v>6</v>
@@ -3091,13 +3115,13 @@
         <v>18</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F73" s="1">
         <v>10</v>
@@ -3111,13 +3135,13 @@
         <v>40</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -3131,13 +3155,13 @@
         <v>29</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F75" s="1">
         <v>5</v>
@@ -3151,13 +3175,13 @@
         <v>8</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F76" s="1">
         <v>3</v>
@@ -3171,13 +3195,13 @@
         <v>32</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F77" s="1">
         <v>5</v>
@@ -3191,13 +3215,13 @@
         <v>40</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F78" s="1">
         <v>5</v>
@@ -3211,13 +3235,13 @@
         <v>40</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F79" s="1">
         <v>3</v>
@@ -3231,13 +3255,13 @@
         <v>18</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F80" s="1">
         <v>10</v>
@@ -3251,13 +3275,13 @@
         <v>8</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F81" s="1">
         <v>6</v>
@@ -3271,13 +3295,13 @@
         <v>47</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F82" s="1">
         <v>6</v>
@@ -3291,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F83" s="1">
         <v>6</v>
@@ -3311,13 +3335,13 @@
         <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="F84" s="1">
         <v>6</v>
@@ -3331,13 +3355,13 @@
         <v>8</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F85" s="1">
         <v>8</v>
@@ -3351,13 +3375,13 @@
         <v>47</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="F86" s="1">
         <v>6</v>
@@ -3371,13 +3395,13 @@
         <v>47</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F87" s="1">
         <v>8</v>
@@ -3391,13 +3415,13 @@
         <v>18</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F88" s="1">
         <v>10</v>
@@ -3411,13 +3435,13 @@
         <v>40</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F89" s="1">
         <v>4</v>
@@ -3431,13 +3455,13 @@
         <v>8</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
@@ -3451,13 +3475,13 @@
         <v>47</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F91" s="1">
         <v>6</v>
@@ -3471,13 +3495,13 @@
         <v>47</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -3491,13 +3515,13 @@
         <v>40</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="F93" s="1">
         <v>4</v>
@@ -3511,13 +3535,13 @@
         <v>29</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F94" s="1">
         <v>5</v>
@@ -3531,13 +3555,13 @@
         <v>18</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F95" s="1">
         <v>2</v>
@@ -3551,13 +3575,13 @@
         <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F96" s="1">
         <v>5</v>
@@ -3571,13 +3595,13 @@
         <v>40</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F97" s="1">
         <v>2</v>
@@ -3591,13 +3615,13 @@
         <v>40</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F98" s="1">
         <v>5</v>
@@ -3611,13 +3635,13 @@
         <v>47</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F99" s="1">
         <v>3</v>
@@ -3631,13 +3655,13 @@
         <v>8</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F100" s="1">
         <v>10</v>
@@ -3651,13 +3675,13 @@
         <v>26</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F101" s="1">
         <v>6</v>
@@ -3671,13 +3695,13 @@
         <v>29</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F102" s="1">
         <v>5</v>
@@ -3691,13 +3715,13 @@
         <v>8</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F103" s="1">
         <v>6</v>
@@ -3711,13 +3735,13 @@
         <v>47</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F104" s="1">
         <v>6</v>
@@ -3731,13 +3755,13 @@
         <v>32</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F105" s="1">
         <v>5</v>
@@ -3751,13 +3775,13 @@
         <v>26</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F106" s="1">
         <v>2</v>
@@ -3771,13 +3795,13 @@
         <v>8</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="F107" s="1">
         <v>3</v>
@@ -3791,13 +3815,13 @@
         <v>8</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F108" s="1">
         <v>10</v>
@@ -3811,13 +3835,13 @@
         <v>47</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="F109" s="1">
         <v>3</v>
@@ -3831,13 +3855,13 @@
         <v>47</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F110" s="1">
         <v>10</v>
@@ -3851,13 +3875,13 @@
         <v>8</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F111" s="1">
         <v>10</v>
@@ -3871,13 +3895,13 @@
         <v>47</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F112" s="1">
         <v>10</v>
@@ -3891,13 +3915,13 @@
         <v>8</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F113" s="1">
         <v>6</v>
@@ -3911,13 +3935,13 @@
         <v>18</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F114" s="1">
         <v>10</v>
@@ -3931,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F115" s="1">
         <v>4</v>
@@ -3951,13 +3975,13 @@
         <v>29</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="F116" s="1">
         <v>6</v>
@@ -3971,13 +3995,13 @@
         <v>18</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F117" s="1">
         <v>35</v>
@@ -3991,13 +4015,13 @@
         <v>32</v>
       </c>
       <c r="C118" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="F118" s="1">
         <v>6</v>
@@ -4011,13 +4035,13 @@
         <v>47</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F119" s="1">
         <v>10</v>
@@ -4031,13 +4055,13 @@
         <v>18</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F120" s="1">
         <v>3</v>
@@ -4051,13 +4075,13 @@
         <v>8</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F121" s="1">
         <v>6</v>
@@ -4071,13 +4095,13 @@
         <v>8</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F122" s="1">
         <v>10</v>
@@ -4091,13 +4115,13 @@
         <v>47</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F123" s="1">
         <v>10</v>
@@ -4111,13 +4135,13 @@
         <v>8</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F124" s="1">
         <v>10</v>
@@ -4131,13 +4155,13 @@
         <v>47</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F125" s="1">
         <v>10</v>
@@ -4151,13 +4175,13 @@
         <v>47</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F126" s="1">
         <v>6</v>
@@ -4171,13 +4195,13 @@
         <v>18</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="F127" s="1">
         <v>5</v>
@@ -4191,13 +4215,13 @@
         <v>18</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F128" s="1">
         <v>3</v>
@@ -4211,13 +4235,13 @@
         <v>47</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F129" s="1">
         <v>6</v>
@@ -4231,13 +4255,13 @@
         <v>47</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F130" s="1">
         <v>6</v>
@@ -4251,13 +4275,13 @@
         <v>18</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F131" s="1">
         <v>50</v>
@@ -4271,13 +4295,13 @@
         <v>47</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F132" s="1">
         <v>6</v>
@@ -4291,13 +4315,13 @@
         <v>47</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F133" s="1">
         <v>10</v>
@@ -4311,13 +4335,13 @@
         <v>47</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F134" s="1">
         <v>10</v>
@@ -4330,7 +4354,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A65:F134 D64:F64 A64:B64 A63:F63 D62:F62 A62:B62 A36:F61 D35:F35 A35:B35 A33:F34 D32:F32 A32:B32 A2:F31 A1 C1:F1" numberStoredAsText="1"/>
+    <ignoredError sqref="C1:F1 A1 A2:F31 A32:B32 D32:F32 A33:F34 A35:B35 D35:F35 A36:F54 A55:B55 D55:F55 A56:F61 A62:B62 D62:F62 A63:F63 A64:B64 D64:F64 A65:F134" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>